--- a/01_Raw_data/Depth_length_velocity_width/velocity.xlsx
+++ b/01_Raw_data/Depth_length_velocity_width/velocity.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\SpringsProject_Sam&amp;Paul\Depth_length_velocity_width\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uflorida-my.sharepoint.com/personal/samanthahowley_ufl_edu/Documents/Desktop/SpringMetabolism_FlowReversals/01_Raw_data/Depth_length_velocity_width/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBDE34AF-19B8-477D-9527-1809E39E3E3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{BBDE34AF-19B8-477D-9527-1809E39E3E3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8AAEF5A-DE12-4C59-BDAE-CEA1A29A5776}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AllenMill" sheetId="1" r:id="rId1"/>
@@ -538,6 +538,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -545,7 +546,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1465,13 +1465,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F19"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.7265625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="20.7265625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1491,7 +1491,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>44742.166666666672</v>
       </c>
@@ -1511,7 +1511,7 @@
         <v>0.36752642087327392</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>44762</v>
       </c>
@@ -1531,7 +1531,7 @@
         <v>0.14650561651333111</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>44789</v>
       </c>
@@ -1551,7 +1551,7 @@
         <v>0.2000660130757792</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>44844</v>
       </c>
@@ -1571,7 +1571,7 @@
         <v>0.3183333637360477</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>44860</v>
       </c>
@@ -1591,7 +1591,7 @@
         <v>0.52371134020618559</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>44865</v>
       </c>
@@ -1611,7 +1611,7 @@
         <v>0.88392000000000004</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>44872</v>
       </c>
@@ -1631,7 +1631,7 @@
         <v>0.32508800559832052</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>44886</v>
       </c>
@@ -1651,7 +1651,7 @@
         <v>0.24384</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>44900</v>
       </c>
@@ -1671,7 +1671,7 @@
         <v>0.39284874334801589</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>44929</v>
       </c>
@@ -1691,7 +1691,7 @@
         <v>0.41148000000000001</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>44944</v>
       </c>
@@ -1711,7 +1711,7 @@
         <v>0.41148000000000001</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>44951</v>
       </c>
@@ -1731,7 +1731,7 @@
         <v>7.5695364238410584E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>44958</v>
       </c>
@@ -1751,7 +1751,7 @@
         <v>9.6864406779661016E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>44972</v>
       </c>
@@ -1771,7 +1771,7 @@
         <v>-2.5907667950055769E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>44986</v>
       </c>
@@ -1791,7 +1791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>45000</v>
       </c>
@@ -1811,7 +1811,7 @@
         <v>8.526759287224403E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>45014</v>
       </c>
@@ -1831,7 +1831,7 @@
         <v>0.1114890928132463</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>45028</v>
       </c>
@@ -1859,12 +1859,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F17"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="5" width="20.7265625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
@@ -1884,7 +1884,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1904,7 +1904,7 @@
         <v>9.9059999999999995E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>0</v>
       </c>
@@ -1924,7 +1924,7 @@
         <v>0.1257639516032511</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>0</v>
       </c>
@@ -1944,7 +1944,7 @@
         <v>6.8341643611171704E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>0</v>
       </c>
@@ -1964,7 +1964,7 @@
         <v>5.9129280697505449E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>0</v>
       </c>
@@ -1984,7 +1984,7 @@
         <v>0.1014934360244453</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>0</v>
       </c>
@@ -2004,7 +2004,7 @@
         <v>0.103632</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>0</v>
       </c>
@@ -2024,7 +2024,7 @@
         <v>0.23330000000000001</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>0</v>
       </c>
@@ -2044,7 +2044,7 @@
         <v>0.257876726</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>0</v>
       </c>
@@ -2064,7 +2064,7 @@
         <v>0.23090909100000001</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>0</v>
       </c>
@@ -2084,7 +2084,7 @@
         <v>9.0472021872482419E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>0</v>
       </c>
@@ -2104,7 +2104,7 @@
         <v>0.13669744500710351</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>0</v>
       </c>
@@ -2124,7 +2124,7 @@
         <v>0.10988906777573069</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>0</v>
       </c>
@@ -2144,7 +2144,7 @@
         <v>7.7164556962025316E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>0</v>
       </c>
@@ -2164,7 +2164,7 @@
         <v>0.12564406432603081</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>0</v>
       </c>
@@ -2184,7 +2184,7 @@
         <v>0.10000388592265851</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>0</v>
       </c>
@@ -2212,13 +2212,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F19"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.7265625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="20.7265625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="22.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.28515625" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -2238,7 +2239,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>44740</v>
       </c>
@@ -2255,7 +2256,7 @@
         <v>44740</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>44747</v>
       </c>
@@ -2272,7 +2273,7 @@
         <v>44747</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>44804</v>
       </c>
@@ -2292,7 +2293,7 @@
         <v>0.21041420118343199</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>44830</v>
       </c>
@@ -2312,7 +2313,7 @@
         <v>8.7832831102109377E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>44844</v>
       </c>
@@ -2332,7 +2333,7 @@
         <v>0.26250863915221118</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>44860</v>
       </c>
@@ -2352,7 +2353,7 @@
         <v>0.38382356367635467</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>44872</v>
       </c>
@@ -2372,7 +2373,7 @@
         <v>0.43940091193109848</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>44886</v>
       </c>
@@ -2392,7 +2393,7 @@
         <v>0.24574982722874911</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>44900</v>
       </c>
@@ -2412,7 +2413,7 @@
         <v>0.31575888663127311</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>44914</v>
       </c>
@@ -2432,7 +2433,7 @@
         <v>0.27092143777075278</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>44929</v>
       </c>
@@ -2452,7 +2453,7 @@
         <v>0.38927203065134097</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>44944</v>
       </c>
@@ -2472,7 +2473,7 @@
         <v>0.24384</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>44958</v>
       </c>
@@ -2492,7 +2493,7 @@
         <v>0.27730699246165852</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>44972</v>
       </c>
@@ -2512,7 +2513,7 @@
         <v>0.15203267905529569</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>44986</v>
       </c>
@@ -2532,7 +2533,7 @@
         <v>9.9617104075948384E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>45000</v>
       </c>
@@ -2552,7 +2553,7 @@
         <v>0.2090435258513042</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>45014</v>
       </c>
@@ -2572,7 +2573,7 @@
         <v>0.1436418572624438</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>45021</v>
       </c>
@@ -2601,13 +2602,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:F19"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.7265625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="20.7265625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2627,7 +2628,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>44742.166666666672</v>
       </c>
@@ -2647,7 +2648,7 @@
         <v>0.36752642087327392</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>44762</v>
       </c>
@@ -2667,7 +2668,7 @@
         <v>0.14650561651333111</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>44789</v>
       </c>
@@ -2687,7 +2688,7 @@
         <v>0.2000660130757792</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>44844</v>
       </c>
@@ -2707,7 +2708,7 @@
         <v>0.3183333637360477</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>44860</v>
       </c>
@@ -2727,7 +2728,7 @@
         <v>0.52371134020618559</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>44865</v>
       </c>
@@ -2747,7 +2748,7 @@
         <v>0.88392000000000004</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>44872</v>
       </c>
@@ -2767,7 +2768,7 @@
         <v>0.32508800559832052</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>44886</v>
       </c>
@@ -2787,7 +2788,7 @@
         <v>0.24384</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>44900</v>
       </c>
@@ -2807,7 +2808,7 @@
         <v>0.39284874334801589</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>44929</v>
       </c>
@@ -2827,7 +2828,7 @@
         <v>0.41148000000000001</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>44944</v>
       </c>
@@ -2847,7 +2848,7 @@
         <v>0.41148000000000001</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>44951</v>
       </c>
@@ -2867,7 +2868,7 @@
         <v>7.5695364238410584E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>44958</v>
       </c>
@@ -2887,7 +2888,7 @@
         <v>9.6864406779661016E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>44972</v>
       </c>
@@ -2907,7 +2908,7 @@
         <v>-2.5907667950055769E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>44986</v>
       </c>
@@ -2927,7 +2928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>45000</v>
       </c>
@@ -2947,7 +2948,7 @@
         <v>8.526759287224403E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>45014</v>
       </c>
@@ -2967,7 +2968,7 @@
         <v>0.1114890928132463</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>45028</v>
       </c>
@@ -2995,13 +2996,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:F18"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.7265625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="20.7265625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3021,7 +3022,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>44747</v>
       </c>
@@ -3041,7 +3042,7 @@
         <v>9.4584565724526684E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>44774</v>
       </c>
@@ -3061,7 +3062,7 @@
         <v>8.1818433179723496E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>44801</v>
       </c>
@@ -3081,7 +3082,7 @@
         <v>0.1836144578313253</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>44830</v>
       </c>
@@ -3101,7 +3102,7 @@
         <v>7.2260979365715627E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>44858</v>
       </c>
@@ -3121,7 +3122,7 @@
         <v>9.0498812351543945E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>44872</v>
       </c>
@@ -3141,7 +3142,7 @@
         <v>7.4432234432234429E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>44886</v>
       </c>
@@ -3161,7 +3162,7 @@
         <v>0.1320518461197363</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>44900</v>
       </c>
@@ -3181,7 +3182,7 @@
         <v>0.16555581048725421</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>44915</v>
       </c>
@@ -3201,7 +3202,7 @@
         <v>7.619999999999999E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>44930</v>
       </c>
@@ -3221,7 +3222,7 @@
         <v>0.13716</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>44944</v>
       </c>
@@ -3241,7 +3242,7 @@
         <v>0.195072</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>44951</v>
       </c>
@@ -3261,7 +3262,7 @@
         <v>0.12192</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>44972</v>
       </c>
@@ -3281,7 +3282,7 @@
         <v>0.176784</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>44986</v>
       </c>
@@ -3301,7 +3302,7 @@
         <v>0.20116800000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>45000</v>
       </c>
@@ -3321,7 +3322,7 @@
         <v>0.20319999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>45014</v>
       </c>
@@ -3341,7 +3342,7 @@
         <v>0.1016</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>45028</v>
       </c>
